--- a/results/q4_output/未来需求推演.xlsx
+++ b/results/q4_output/未来需求推演.xlsx
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17977.70078277588</v>
+        <v>3653.258806228638</v>
       </c>
       <c r="F2" t="n">
-        <v>1962.439331054688</v>
+        <v>294.4512023925781</v>
       </c>
     </row>
     <row r="3">
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16926.73729515076</v>
+        <v>3364.210585594177</v>
       </c>
       <c r="F3" t="n">
-        <v>2213.71337890625</v>
+        <v>288.5391845703125</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16488.24035525322</v>
+        <v>3098.786395549774</v>
       </c>
       <c r="F4" t="n">
-        <v>1951.3349609375</v>
+        <v>275.9095458984375</v>
       </c>
     </row>
     <row r="5">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16183.32241249084</v>
+        <v>3055.419787526131</v>
       </c>
       <c r="F5" t="n">
-        <v>1758.646606445312</v>
+        <v>266.1549682617188</v>
       </c>
     </row>
     <row r="6">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15582.0695605278</v>
+        <v>2876.578818738461</v>
       </c>
       <c r="F6" t="n">
-        <v>1783.058837890625</v>
+        <v>283.1046142578125</v>
       </c>
     </row>
     <row r="7">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15392.66575288773</v>
+        <v>2769.789909601212</v>
       </c>
       <c r="F7" t="n">
-        <v>2008.546997070312</v>
+        <v>272.9317626953125</v>
       </c>
     </row>
     <row r="8">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12424.57675504684</v>
+        <v>1857.373454928398</v>
       </c>
       <c r="F8" t="n">
-        <v>1540.460083007812</v>
+        <v>237.9653625488281</v>
       </c>
     </row>
     <row r="9">
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9261.790073394775</v>
+        <v>1831.255016922951</v>
       </c>
       <c r="F9" t="n">
-        <v>952.9539794921875</v>
+        <v>245.369140625</v>
       </c>
     </row>
     <row r="10">
@@ -670,10 +670,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8220.167894363403</v>
+        <v>1831.255016922951</v>
       </c>
       <c r="F10" t="n">
-        <v>1135.307739257812</v>
+        <v>245.369140625</v>
       </c>
     </row>
     <row r="11">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7517.253492355347</v>
+        <v>1749.226257532835</v>
       </c>
       <c r="F11" t="n">
-        <v>894.250244140625</v>
+        <v>230.1560668945312</v>
       </c>
     </row>
     <row r="12">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>19775.47086105347</v>
+        <v>4018.584686851502</v>
       </c>
       <c r="F12" t="n">
-        <v>2158.683264160157</v>
+        <v>323.896322631836</v>
       </c>
     </row>
     <row r="13">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>18619.41102466584</v>
+        <v>3700.631644153595</v>
       </c>
       <c r="F13" t="n">
-        <v>2435.084716796875</v>
+        <v>317.3931030273438</v>
       </c>
     </row>
     <row r="14">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18137.06439077854</v>
+        <v>3408.665035104752</v>
       </c>
       <c r="F14" t="n">
-        <v>2146.46845703125</v>
+        <v>303.5005004882813</v>
       </c>
     </row>
     <row r="15">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>17801.65465373993</v>
+        <v>3360.961766278745</v>
       </c>
       <c r="F15" t="n">
-        <v>1934.511267089843</v>
+        <v>292.7704650878907</v>
       </c>
     </row>
     <row r="16">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>17140.27651658058</v>
+        <v>3164.236700612307</v>
       </c>
       <c r="F16" t="n">
-        <v>1961.364721679688</v>
+        <v>311.4150756835938</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16931.9323281765</v>
+        <v>3046.768900561333</v>
       </c>
       <c r="F17" t="n">
-        <v>2209.401696777343</v>
+        <v>300.2249389648438</v>
       </c>
     </row>
     <row r="18">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13667.03443055153</v>
+        <v>2043.110800421238</v>
       </c>
       <c r="F18" t="n">
-        <v>1694.506091308593</v>
+        <v>261.7618988037109</v>
       </c>
     </row>
     <row r="19">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10187.96908073425</v>
+        <v>2014.380518615246</v>
       </c>
       <c r="F19" t="n">
-        <v>1048.249377441406</v>
+        <v>269.9060546875</v>
       </c>
     </row>
     <row r="20">
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9042.184683799744</v>
+        <v>2014.380518615246</v>
       </c>
       <c r="F20" t="n">
-        <v>1248.838513183593</v>
+        <v>269.9060546875</v>
       </c>
     </row>
     <row r="21">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8268.978841590882</v>
+        <v>1924.148883286119</v>
       </c>
       <c r="F21" t="n">
-        <v>983.6752685546876</v>
+        <v>253.1716735839843</v>
       </c>
     </row>
     <row r="22">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21753.01794715882</v>
+        <v>4420.443155536653</v>
       </c>
       <c r="F22" t="n">
-        <v>2374.551590576173</v>
+        <v>356.2859548950196</v>
       </c>
     </row>
     <row r="23">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20481.35212713242</v>
+        <v>4070.694808568955</v>
       </c>
       <c r="F23" t="n">
-        <v>2678.593188476563</v>
+        <v>349.1324133300782</v>
       </c>
     </row>
     <row r="24">
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>19950.7708298564</v>
+        <v>3749.531538615227</v>
       </c>
       <c r="F24" t="n">
-        <v>2361.115302734375</v>
+        <v>333.8505505371094</v>
       </c>
     </row>
     <row r="25">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>19581.82011911392</v>
+        <v>3697.057942906619</v>
       </c>
       <c r="F25" t="n">
-        <v>2127.962393798828</v>
+        <v>322.0475115966798</v>
       </c>
     </row>
     <row r="26">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>18854.30416823864</v>
+        <v>3480.660370673538</v>
       </c>
       <c r="F26" t="n">
-        <v>2157.501193847656</v>
+        <v>342.5565832519532</v>
       </c>
     </row>
     <row r="27">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>18625.12556099415</v>
+        <v>3351.445790617467</v>
       </c>
       <c r="F27" t="n">
-        <v>2430.341866455078</v>
+        <v>330.2474328613282</v>
       </c>
     </row>
     <row r="28">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>15033.73787360668</v>
+        <v>2247.421880463362</v>
       </c>
       <c r="F28" t="n">
-        <v>1863.956700439453</v>
+        <v>287.9380886840821</v>
       </c>
     </row>
     <row r="29">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11206.76598880768</v>
+        <v>2215.818570476771</v>
       </c>
       <c r="F29" t="n">
-        <v>1153.074315185547</v>
+        <v>296.8966601562501</v>
       </c>
     </row>
     <row r="30">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9946.403152179719</v>
+        <v>2215.818570476771</v>
       </c>
       <c r="F30" t="n">
-        <v>1373.722364501953</v>
+        <v>296.8966601562501</v>
       </c>
     </row>
     <row r="31">
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9095.876725749971</v>
+        <v>2116.563771614731</v>
       </c>
       <c r="F31" t="n">
-        <v>1082.042795410156</v>
+        <v>278.4888409423828</v>
       </c>
     </row>
     <row r="32">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>17977.70078277588</v>
+        <v>3653.258806228638</v>
       </c>
       <c r="F32" t="n">
-        <v>1962.439331054688</v>
+        <v>294.4512023925781</v>
       </c>
     </row>
     <row r="33">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>16926.73729515076</v>
+        <v>3364.210585594177</v>
       </c>
       <c r="F33" t="n">
-        <v>2213.71337890625</v>
+        <v>288.5391845703125</v>
       </c>
     </row>
     <row r="34">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>16488.24035525322</v>
+        <v>3098.786395549774</v>
       </c>
       <c r="F34" t="n">
-        <v>1951.3349609375</v>
+        <v>275.9095458984375</v>
       </c>
     </row>
     <row r="35">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>16183.32241249084</v>
+        <v>3055.419787526131</v>
       </c>
       <c r="F35" t="n">
-        <v>1758.646606445312</v>
+        <v>266.1549682617188</v>
       </c>
     </row>
     <row r="36">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>15582.0695605278</v>
+        <v>2876.578818738461</v>
       </c>
       <c r="F36" t="n">
-        <v>1783.058837890625</v>
+        <v>283.1046142578125</v>
       </c>
     </row>
     <row r="37">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15392.66575288773</v>
+        <v>2769.789909601212</v>
       </c>
       <c r="F37" t="n">
-        <v>2008.546997070312</v>
+        <v>272.9317626953125</v>
       </c>
     </row>
     <row r="38">
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>12424.57675504684</v>
+        <v>1857.373454928398</v>
       </c>
       <c r="F38" t="n">
-        <v>1540.460083007812</v>
+        <v>237.9653625488281</v>
       </c>
     </row>
     <row r="39">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>9261.790073394775</v>
+        <v>1831.255016922951</v>
       </c>
       <c r="F39" t="n">
-        <v>952.9539794921875</v>
+        <v>245.369140625</v>
       </c>
     </row>
     <row r="40">
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8220.167894363403</v>
+        <v>1831.255016922951</v>
       </c>
       <c r="F40" t="n">
-        <v>1135.307739257812</v>
+        <v>245.369140625</v>
       </c>
     </row>
     <row r="41">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7517.253492355347</v>
+        <v>1749.226257532835</v>
       </c>
       <c r="F41" t="n">
-        <v>894.250244140625</v>
+        <v>230.1560668945312</v>
       </c>
     </row>
     <row r="42">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>20674.35590019226</v>
+        <v>4201.247627162934</v>
       </c>
       <c r="F42" t="n">
-        <v>2256.805230712891</v>
+        <v>338.6188827514648</v>
       </c>
     </row>
     <row r="43">
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>19465.74788942337</v>
+        <v>3868.842173433303</v>
       </c>
       <c r="F43" t="n">
-        <v>2545.770385742188</v>
+        <v>331.8200622558593</v>
       </c>
     </row>
     <row r="44">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18961.4764085412</v>
+        <v>3563.60435488224</v>
       </c>
       <c r="F44" t="n">
-        <v>2244.035205078125</v>
+        <v>317.2959777832031</v>
       </c>
     </row>
     <row r="45">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>18610.82077436446</v>
+        <v>3513.73275565505</v>
       </c>
       <c r="F45" t="n">
-        <v>2022.443597412109</v>
+        <v>306.0782135009766</v>
       </c>
     </row>
     <row r="46">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17919.37999460697</v>
+        <v>3308.06564154923</v>
       </c>
       <c r="F46" t="n">
-        <v>2050.517663574219</v>
+        <v>325.5703063964843</v>
       </c>
     </row>
     <row r="47">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17701.56561582089</v>
+        <v>3185.258396041394</v>
       </c>
       <c r="F47" t="n">
-        <v>2309.829046630859</v>
+        <v>313.8715270996094</v>
       </c>
     </row>
     <row r="48">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>14288.26326830387</v>
+        <v>2135.979473167657</v>
       </c>
       <c r="F48" t="n">
-        <v>1771.529095458984</v>
+        <v>273.6601669311523</v>
       </c>
     </row>
     <row r="49">
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10651.05858440399</v>
+        <v>2105.943269461393</v>
       </c>
       <c r="F49" t="n">
-        <v>1095.897076416016</v>
+        <v>282.17451171875</v>
       </c>
     </row>
     <row r="50">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9453.193078517914</v>
+        <v>2105.943269461393</v>
       </c>
       <c r="F50" t="n">
-        <v>1305.603900146484</v>
+        <v>282.17451171875</v>
       </c>
     </row>
     <row r="51">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8644.841516208648</v>
+        <v>2011.61019616276</v>
       </c>
       <c r="F51" t="n">
-        <v>1028.387780761719</v>
+        <v>264.6794769287109</v>
       </c>
     </row>
     <row r="52">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>23775.50928522109</v>
+        <v>4831.434771237373</v>
       </c>
       <c r="F52" t="n">
-        <v>2595.326015319824</v>
+        <v>389.4117151641845</v>
       </c>
     </row>
     <row r="53">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>22385.61007283688</v>
+        <v>4449.168499448298</v>
       </c>
       <c r="F53" t="n">
-        <v>2927.635943603515</v>
+        <v>381.5930715942382</v>
       </c>
     </row>
     <row r="54">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>21805.69786982238</v>
+        <v>4098.145008114576</v>
       </c>
       <c r="F54" t="n">
-        <v>2580.640485839843</v>
+        <v>364.8903744506835</v>
       </c>
     </row>
     <row r="55">
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>21402.44389051913</v>
+        <v>4040.792669003308</v>
       </c>
       <c r="F55" t="n">
-        <v>2325.810137023925</v>
+        <v>351.9899455261231</v>
       </c>
     </row>
     <row r="56">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20607.28699379801</v>
+        <v>3804.275487781614</v>
       </c>
       <c r="F56" t="n">
-        <v>2358.095313110351</v>
+        <v>374.405852355957</v>
       </c>
     </row>
     <row r="57">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>20356.80045819402</v>
+        <v>3663.047155447602</v>
       </c>
       <c r="F57" t="n">
-        <v>2656.303403625487</v>
+        <v>360.9522561645507</v>
       </c>
     </row>
     <row r="58">
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>16431.50275854944</v>
+        <v>2456.376394142806</v>
       </c>
       <c r="F58" t="n">
-        <v>2037.258459777831</v>
+        <v>314.7091919708251</v>
       </c>
     </row>
     <row r="59">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>12248.71737206459</v>
+        <v>2421.834759880602</v>
       </c>
       <c r="F59" t="n">
-        <v>1260.281637878418</v>
+        <v>324.5006884765625</v>
       </c>
     </row>
     <row r="60">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>10871.1720402956</v>
+        <v>2421.834759880602</v>
       </c>
       <c r="F60" t="n">
-        <v>1501.444485168456</v>
+        <v>324.5006884765625</v>
       </c>
     </row>
     <row r="61">
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>9941.567743639944</v>
+        <v>2313.351725587174</v>
       </c>
       <c r="F61" t="n">
-        <v>1182.645947875976</v>
+        <v>304.3813984680174</v>
       </c>
     </row>
     <row r="62">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>17977.70078277588</v>
+        <v>3653.258806228638</v>
       </c>
       <c r="F62" t="n">
-        <v>1962.439331054688</v>
+        <v>294.4512023925781</v>
       </c>
     </row>
     <row r="63">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>16926.73729515076</v>
+        <v>3364.210585594177</v>
       </c>
       <c r="F63" t="n">
-        <v>2213.71337890625</v>
+        <v>288.5391845703125</v>
       </c>
     </row>
     <row r="64">
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>16488.24035525322</v>
+        <v>3098.786395549774</v>
       </c>
       <c r="F64" t="n">
-        <v>1951.3349609375</v>
+        <v>275.9095458984375</v>
       </c>
     </row>
     <row r="65">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>16183.32241249084</v>
+        <v>3055.419787526131</v>
       </c>
       <c r="F65" t="n">
-        <v>1758.646606445312</v>
+        <v>266.1549682617188</v>
       </c>
     </row>
     <row r="66">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>15582.0695605278</v>
+        <v>2876.578818738461</v>
       </c>
       <c r="F66" t="n">
-        <v>1783.058837890625</v>
+        <v>283.1046142578125</v>
       </c>
     </row>
     <row r="67">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>15392.66575288773</v>
+        <v>2769.789909601212</v>
       </c>
       <c r="F67" t="n">
-        <v>2008.546997070312</v>
+        <v>272.9317626953125</v>
       </c>
     </row>
     <row r="68">
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>12424.57675504684</v>
+        <v>1857.373454928398</v>
       </c>
       <c r="F68" t="n">
-        <v>1540.460083007812</v>
+        <v>237.9653625488281</v>
       </c>
     </row>
     <row r="69">
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>9261.790073394775</v>
+        <v>1831.255016922951</v>
       </c>
       <c r="F69" t="n">
-        <v>952.9539794921875</v>
+        <v>245.369140625</v>
       </c>
     </row>
     <row r="70">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8220.167894363403</v>
+        <v>1831.255016922951</v>
       </c>
       <c r="F70" t="n">
-        <v>1135.307739257812</v>
+        <v>245.369140625</v>
       </c>
     </row>
     <row r="71">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>7517.253492355347</v>
+        <v>1749.226257532835</v>
       </c>
       <c r="F71" t="n">
-        <v>894.250244140625</v>
+        <v>230.1560668945312</v>
       </c>
     </row>
     <row r="72">
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21573.24093933106</v>
+        <v>4383.910567474366</v>
       </c>
       <c r="F72" t="n">
-        <v>2354.927197265626</v>
+        <v>353.3414428710938</v>
       </c>
     </row>
     <row r="73">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>20312.08475418091</v>
+        <v>4037.052702713012</v>
       </c>
       <c r="F73" t="n">
-        <v>2656.4560546875</v>
+        <v>346.247021484375</v>
       </c>
     </row>
     <row r="74">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>19785.88842630386</v>
+        <v>3718.543674659729</v>
       </c>
       <c r="F74" t="n">
-        <v>2341.601953125</v>
+        <v>331.091455078125</v>
       </c>
     </row>
     <row r="75">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>19419.98689498901</v>
+        <v>3666.503745031357</v>
       </c>
       <c r="F75" t="n">
-        <v>2110.375927734374</v>
+        <v>319.3859619140625</v>
       </c>
     </row>
     <row r="76">
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>18698.48347263336</v>
+        <v>3451.894582486153</v>
       </c>
       <c r="F76" t="n">
-        <v>2139.67060546875</v>
+        <v>339.725537109375</v>
       </c>
     </row>
     <row r="77">
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>18471.19890346528</v>
+        <v>3323.747891521454</v>
       </c>
       <c r="F77" t="n">
-        <v>2410.256396484374</v>
+        <v>327.518115234375</v>
       </c>
     </row>
     <row r="78">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>14909.49210605621</v>
+        <v>2228.848145914078</v>
       </c>
       <c r="F78" t="n">
-        <v>1848.552099609374</v>
+        <v>285.5584350585937</v>
       </c>
     </row>
     <row r="79">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>11114.14808807373</v>
+        <v>2197.506020307541</v>
       </c>
       <c r="F79" t="n">
-        <v>1143.544775390625</v>
+        <v>294.44296875</v>
       </c>
     </row>
     <row r="80">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>9864.201473236084</v>
+        <v>2197.506020307541</v>
       </c>
       <c r="F80" t="n">
-        <v>1362.369287109374</v>
+        <v>294.44296875</v>
       </c>
     </row>
     <row r="81">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>9020.704190826416</v>
+        <v>2099.071509039402</v>
       </c>
       <c r="F81" t="n">
-        <v>1073.10029296875</v>
+        <v>276.1872802734374</v>
       </c>
     </row>
     <row r="82">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>25887.88912719726</v>
+        <v>5260.692680969239</v>
       </c>
       <c r="F82" t="n">
-        <v>2825.91263671875</v>
+        <v>424.0097314453125</v>
       </c>
     </row>
     <row r="83">
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24374.50170501709</v>
+        <v>4844.463243255615</v>
       </c>
       <c r="F83" t="n">
-        <v>3187.747265625</v>
+        <v>415.49642578125</v>
       </c>
     </row>
     <row r="84">
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>23743.06611156464</v>
+        <v>4462.252409591674</v>
       </c>
       <c r="F84" t="n">
-        <v>2809.92234375</v>
+        <v>397.30974609375</v>
       </c>
     </row>
     <row r="85">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>23303.98427398681</v>
+        <v>4399.804494037629</v>
       </c>
       <c r="F85" t="n">
-        <v>2532.451113281249</v>
+        <v>383.2631542968751</v>
       </c>
     </row>
     <row r="86">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>22438.18016716003</v>
+        <v>4142.273498983383</v>
       </c>
       <c r="F86" t="n">
-        <v>2567.6047265625</v>
+        <v>407.67064453125</v>
       </c>
     </row>
     <row r="87">
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>22165.43868415833</v>
+        <v>3988.497469825745</v>
       </c>
       <c r="F87" t="n">
-        <v>2892.307675781249</v>
+        <v>393.02173828125</v>
       </c>
     </row>
     <row r="88">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>17891.39052726745</v>
+        <v>2674.617775096893</v>
       </c>
       <c r="F88" t="n">
-        <v>2218.262519531249</v>
+        <v>342.6701220703125</v>
       </c>
     </row>
     <row r="89">
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>13336.97770568848</v>
+        <v>2637.007224369049</v>
       </c>
       <c r="F89" t="n">
-        <v>1372.25373046875</v>
+        <v>353.3315625</v>
       </c>
     </row>
     <row r="90">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>11837.0417678833</v>
+        <v>2637.007224369049</v>
       </c>
       <c r="F90" t="n">
-        <v>1634.843144531249</v>
+        <v>353.3315625</v>
       </c>
     </row>
     <row r="91">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>10824.8450289917</v>
+        <v>2518.885810847282</v>
       </c>
       <c r="F91" t="n">
-        <v>1287.7203515625</v>
+        <v>331.4247363281249</v>
       </c>
     </row>
   </sheetData>

--- a/results/q4_output/未来需求推演.xlsx
+++ b/results/q4_output/未来需求推演.xlsx
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3653.258806228638</v>
+        <v>25035.2265625</v>
       </c>
       <c r="F2" t="n">
-        <v>294.4512023925781</v>
+        <v>1781.177001953125</v>
       </c>
     </row>
     <row r="3">
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3364.210585594177</v>
+        <v>23233.1640625</v>
       </c>
       <c r="F3" t="n">
-        <v>288.5391845703125</v>
+        <v>1821.574096679688</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3098.786395549774</v>
+        <v>22607.12109375</v>
       </c>
       <c r="F4" t="n">
-        <v>275.9095458984375</v>
+        <v>2046.7705078125</v>
       </c>
     </row>
     <row r="5">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3055.419787526131</v>
+        <v>19879.025390625</v>
       </c>
       <c r="F5" t="n">
-        <v>266.1549682617188</v>
+        <v>2044.526977539062</v>
       </c>
     </row>
     <row r="6">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2876.578818738461</v>
+        <v>16208.5341796875</v>
       </c>
       <c r="F6" t="n">
-        <v>283.1046142578125</v>
+        <v>1538.9375</v>
       </c>
     </row>
     <row r="7">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2769.789909601212</v>
+        <v>12749.3369140625</v>
       </c>
       <c r="F7" t="n">
-        <v>272.9317626953125</v>
+        <v>840.0941162109375</v>
       </c>
     </row>
     <row r="8">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1857.373454928398</v>
+        <v>6033.43994140625</v>
       </c>
       <c r="F8" t="n">
-        <v>237.9653625488281</v>
+        <v>554.9016723632812</v>
       </c>
     </row>
     <row r="9">
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1831.255016922951</v>
+        <v>5860.44287109375</v>
       </c>
       <c r="F9" t="n">
-        <v>245.369140625</v>
+        <v>848.1298828125</v>
       </c>
     </row>
     <row r="10">
@@ -670,10 +670,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1831.255016922951</v>
+        <v>1718.232177734375</v>
       </c>
       <c r="F10" t="n">
-        <v>245.369140625</v>
+        <v>207.1872711181641</v>
       </c>
     </row>
     <row r="11">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1749.226257532835</v>
+        <v>354.7342529296875</v>
       </c>
       <c r="F11" t="n">
-        <v>230.1560668945312</v>
+        <v>68.81431579589844</v>
       </c>
     </row>
     <row r="12">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4018.584686851502</v>
+        <v>27538.74921875</v>
       </c>
       <c r="F12" t="n">
-        <v>323.896322631836</v>
+        <v>1959.294702148438</v>
       </c>
     </row>
     <row r="13">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3700.631644153595</v>
+        <v>25556.48046875</v>
       </c>
       <c r="F13" t="n">
-        <v>317.3931030273438</v>
+        <v>2003.731506347657</v>
       </c>
     </row>
     <row r="14">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3408.665035104752</v>
+        <v>24867.833203125</v>
       </c>
       <c r="F14" t="n">
-        <v>303.5005004882813</v>
+        <v>2251.44755859375</v>
       </c>
     </row>
     <row r="15">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3360.961766278745</v>
+        <v>21866.9279296875</v>
       </c>
       <c r="F15" t="n">
-        <v>292.7704650878907</v>
+        <v>2248.979675292968</v>
       </c>
     </row>
     <row r="16">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3164.236700612307</v>
+        <v>17829.38759765625</v>
       </c>
       <c r="F16" t="n">
-        <v>311.4150756835938</v>
+        <v>1692.83125</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3046.768900561333</v>
+        <v>14024.27060546875</v>
       </c>
       <c r="F17" t="n">
-        <v>300.2249389648438</v>
+        <v>924.1035278320313</v>
       </c>
     </row>
     <row r="18">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2043.110800421238</v>
+        <v>6636.783935546876</v>
       </c>
       <c r="F18" t="n">
-        <v>261.7618988037109</v>
+        <v>610.3918395996094</v>
       </c>
     </row>
     <row r="19">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2014.380518615246</v>
+        <v>6446.487158203126</v>
       </c>
       <c r="F19" t="n">
-        <v>269.9060546875</v>
+        <v>932.9428710937501</v>
       </c>
     </row>
     <row r="20">
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014.380518615246</v>
+        <v>1890.055395507813</v>
       </c>
       <c r="F20" t="n">
-        <v>269.9060546875</v>
+        <v>227.9059982299805</v>
       </c>
     </row>
     <row r="21">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1924.148883286119</v>
+        <v>390.2076782226563</v>
       </c>
       <c r="F21" t="n">
-        <v>253.1716735839843</v>
+        <v>75.69574737548828</v>
       </c>
     </row>
     <row r="22">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4420.443155536653</v>
+        <v>30292.624140625</v>
       </c>
       <c r="F22" t="n">
-        <v>356.2859548950196</v>
+        <v>2155.224172363281</v>
       </c>
     </row>
     <row r="23">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4070.694808568955</v>
+        <v>28112.12851562501</v>
       </c>
       <c r="F23" t="n">
-        <v>349.1324133300782</v>
+        <v>2204.104656982423</v>
       </c>
     </row>
     <row r="24">
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3749.531538615227</v>
+        <v>27354.6165234375</v>
       </c>
       <c r="F24" t="n">
-        <v>333.8505505371094</v>
+        <v>2476.592314453125</v>
       </c>
     </row>
     <row r="25">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3697.057942906619</v>
+        <v>24053.62072265625</v>
       </c>
       <c r="F25" t="n">
-        <v>322.0475115966798</v>
+        <v>2473.877642822265</v>
       </c>
     </row>
     <row r="26">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3480.660370673538</v>
+        <v>19612.32635742188</v>
       </c>
       <c r="F26" t="n">
-        <v>342.5565832519532</v>
+        <v>1862.114375</v>
       </c>
     </row>
     <row r="27">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3351.445790617467</v>
+        <v>15426.69766601563</v>
       </c>
       <c r="F27" t="n">
-        <v>330.2474328613282</v>
+        <v>1016.513880615234</v>
       </c>
     </row>
     <row r="28">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2247.421880463362</v>
+        <v>7300.462329101563</v>
       </c>
       <c r="F28" t="n">
-        <v>287.9380886840821</v>
+        <v>671.4310235595705</v>
       </c>
     </row>
     <row r="29">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2215.818570476771</v>
+        <v>7091.135874023438</v>
       </c>
       <c r="F29" t="n">
-        <v>296.8966601562501</v>
+        <v>1026.237158203125</v>
       </c>
     </row>
     <row r="30">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2215.818570476771</v>
+        <v>2079.060935058594</v>
       </c>
       <c r="F30" t="n">
-        <v>296.8966601562501</v>
+        <v>250.6965980529786</v>
       </c>
     </row>
     <row r="31">
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2116.563771614731</v>
+        <v>429.228446044922</v>
       </c>
       <c r="F31" t="n">
-        <v>278.4888409423828</v>
+        <v>83.26532211303713</v>
       </c>
     </row>
     <row r="32">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3653.258806228638</v>
+        <v>25035.2265625</v>
       </c>
       <c r="F32" t="n">
-        <v>294.4512023925781</v>
+        <v>1781.177001953125</v>
       </c>
     </row>
     <row r="33">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3364.210585594177</v>
+        <v>23233.1640625</v>
       </c>
       <c r="F33" t="n">
-        <v>288.5391845703125</v>
+        <v>1821.574096679688</v>
       </c>
     </row>
     <row r="34">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3098.786395549774</v>
+        <v>22607.12109375</v>
       </c>
       <c r="F34" t="n">
-        <v>275.9095458984375</v>
+        <v>2046.7705078125</v>
       </c>
     </row>
     <row r="35">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3055.419787526131</v>
+        <v>19879.025390625</v>
       </c>
       <c r="F35" t="n">
-        <v>266.1549682617188</v>
+        <v>2044.526977539062</v>
       </c>
     </row>
     <row r="36">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2876.578818738461</v>
+        <v>16208.5341796875</v>
       </c>
       <c r="F36" t="n">
-        <v>283.1046142578125</v>
+        <v>1538.9375</v>
       </c>
     </row>
     <row r="37">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2769.789909601212</v>
+        <v>12749.3369140625</v>
       </c>
       <c r="F37" t="n">
-        <v>272.9317626953125</v>
+        <v>840.0941162109375</v>
       </c>
     </row>
     <row r="38">
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1857.373454928398</v>
+        <v>6033.43994140625</v>
       </c>
       <c r="F38" t="n">
-        <v>237.9653625488281</v>
+        <v>554.9016723632812</v>
       </c>
     </row>
     <row r="39">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1831.255016922951</v>
+        <v>5860.44287109375</v>
       </c>
       <c r="F39" t="n">
-        <v>245.369140625</v>
+        <v>848.1298828125</v>
       </c>
     </row>
     <row r="40">
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1831.255016922951</v>
+        <v>1718.232177734375</v>
       </c>
       <c r="F40" t="n">
-        <v>245.369140625</v>
+        <v>207.1872711181641</v>
       </c>
     </row>
     <row r="41">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1749.226257532835</v>
+        <v>354.7342529296875</v>
       </c>
       <c r="F41" t="n">
-        <v>230.1560668945312</v>
+        <v>68.81431579589844</v>
       </c>
     </row>
     <row r="42">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4201.247627162934</v>
+        <v>28790.510546875</v>
       </c>
       <c r="F42" t="n">
-        <v>338.6188827514648</v>
+        <v>2048.353552246093</v>
       </c>
     </row>
     <row r="43">
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3868.842173433303</v>
+        <v>26718.138671875</v>
       </c>
       <c r="F43" t="n">
-        <v>331.8200622558593</v>
+        <v>2094.810211181641</v>
       </c>
     </row>
     <row r="44">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3563.60435488224</v>
+        <v>25998.1892578125</v>
       </c>
       <c r="F44" t="n">
-        <v>317.2959777832031</v>
+        <v>2353.786083984375</v>
       </c>
     </row>
     <row r="45">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3513.73275565505</v>
+        <v>22860.87919921875</v>
       </c>
       <c r="F45" t="n">
-        <v>306.0782135009766</v>
+        <v>2351.206024169921</v>
       </c>
     </row>
     <row r="46">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3308.06564154923</v>
+        <v>18639.81430664062</v>
       </c>
       <c r="F46" t="n">
-        <v>325.5703063964843</v>
+        <v>1769.778125</v>
       </c>
     </row>
     <row r="47">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3185.258396041394</v>
+        <v>14661.73745117187</v>
       </c>
       <c r="F47" t="n">
-        <v>313.8715270996094</v>
+        <v>966.1082336425781</v>
       </c>
     </row>
     <row r="48">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2135.979473167657</v>
+        <v>6938.455932617187</v>
       </c>
       <c r="F48" t="n">
-        <v>273.6601669311523</v>
+        <v>638.1369232177734</v>
       </c>
     </row>
     <row r="49">
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2105.943269461393</v>
+        <v>6739.509301757812</v>
       </c>
       <c r="F49" t="n">
-        <v>282.17451171875</v>
+        <v>975.3493652343749</v>
       </c>
     </row>
     <row r="50">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2105.943269461393</v>
+        <v>1975.967004394531</v>
       </c>
       <c r="F50" t="n">
-        <v>282.17451171875</v>
+        <v>238.2653617858887</v>
       </c>
     </row>
     <row r="51">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2011.61019616276</v>
+        <v>407.9443908691406</v>
       </c>
       <c r="F51" t="n">
-        <v>264.6794769287109</v>
+        <v>79.1364631652832</v>
       </c>
     </row>
     <row r="52">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4831.434771237373</v>
+        <v>33109.08712890624</v>
       </c>
       <c r="F52" t="n">
-        <v>389.4117151641845</v>
+        <v>2355.606585083007</v>
       </c>
     </row>
     <row r="53">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4449.168499448298</v>
+        <v>30725.85947265624</v>
       </c>
       <c r="F53" t="n">
-        <v>381.5930715942382</v>
+        <v>2409.031742858887</v>
       </c>
     </row>
     <row r="54">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4098.145008114576</v>
+        <v>29897.91764648437</v>
       </c>
       <c r="F54" t="n">
-        <v>364.8903744506835</v>
+        <v>2706.853996582031</v>
       </c>
     </row>
     <row r="55">
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4040.792669003308</v>
+        <v>26290.01107910156</v>
       </c>
       <c r="F55" t="n">
-        <v>351.9899455261231</v>
+        <v>2703.886927795409</v>
       </c>
     </row>
     <row r="56">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3804.275487781614</v>
+        <v>21435.78645263672</v>
       </c>
       <c r="F56" t="n">
-        <v>374.405852355957</v>
+        <v>2035.24484375</v>
       </c>
     </row>
     <row r="57">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3663.047155447602</v>
+        <v>16860.99806884765</v>
       </c>
       <c r="F57" t="n">
-        <v>360.9522561645507</v>
+        <v>1111.024468688965</v>
       </c>
     </row>
     <row r="58">
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2456.376394142806</v>
+        <v>7979.224322509765</v>
       </c>
       <c r="F58" t="n">
-        <v>314.7091919708251</v>
+        <v>733.8574617004393</v>
       </c>
     </row>
     <row r="59">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2421.834759880602</v>
+        <v>7750.435697021483</v>
       </c>
       <c r="F59" t="n">
-        <v>324.5006884765625</v>
+        <v>1121.651770019531</v>
       </c>
     </row>
     <row r="60">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2421.834759880602</v>
+        <v>2272.362055053711</v>
       </c>
       <c r="F60" t="n">
-        <v>324.5006884765625</v>
+        <v>274.005166053772</v>
       </c>
     </row>
     <row r="61">
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2313.351725587174</v>
+        <v>469.1360494995117</v>
       </c>
       <c r="F61" t="n">
-        <v>304.3813984680174</v>
+        <v>91.00693264007568</v>
       </c>
     </row>
     <row r="62">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3653.258806228638</v>
+        <v>25035.2265625</v>
       </c>
       <c r="F62" t="n">
-        <v>294.4512023925781</v>
+        <v>1781.177001953125</v>
       </c>
     </row>
     <row r="63">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3364.210585594177</v>
+        <v>23233.1640625</v>
       </c>
       <c r="F63" t="n">
-        <v>288.5391845703125</v>
+        <v>1821.574096679688</v>
       </c>
     </row>
     <row r="64">
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3098.786395549774</v>
+        <v>22607.12109375</v>
       </c>
       <c r="F64" t="n">
-        <v>275.9095458984375</v>
+        <v>2046.7705078125</v>
       </c>
     </row>
     <row r="65">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3055.419787526131</v>
+        <v>19879.025390625</v>
       </c>
       <c r="F65" t="n">
-        <v>266.1549682617188</v>
+        <v>2044.526977539062</v>
       </c>
     </row>
     <row r="66">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2876.578818738461</v>
+        <v>16208.5341796875</v>
       </c>
       <c r="F66" t="n">
-        <v>283.1046142578125</v>
+        <v>1538.9375</v>
       </c>
     </row>
     <row r="67">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2769.789909601212</v>
+        <v>12749.3369140625</v>
       </c>
       <c r="F67" t="n">
-        <v>272.9317626953125</v>
+        <v>840.0941162109375</v>
       </c>
     </row>
     <row r="68">
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1857.373454928398</v>
+        <v>6033.43994140625</v>
       </c>
       <c r="F68" t="n">
-        <v>237.9653625488281</v>
+        <v>554.9016723632812</v>
       </c>
     </row>
     <row r="69">
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1831.255016922951</v>
+        <v>5860.44287109375</v>
       </c>
       <c r="F69" t="n">
-        <v>245.369140625</v>
+        <v>848.1298828125</v>
       </c>
     </row>
     <row r="70">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1831.255016922951</v>
+        <v>1718.232177734375</v>
       </c>
       <c r="F70" t="n">
-        <v>245.369140625</v>
+        <v>207.1872711181641</v>
       </c>
     </row>
     <row r="71">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1749.226257532835</v>
+        <v>354.7342529296875</v>
       </c>
       <c r="F71" t="n">
-        <v>230.1560668945312</v>
+        <v>68.81431579589844</v>
       </c>
     </row>
     <row r="72">
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4383.910567474366</v>
+        <v>30042.271875</v>
       </c>
       <c r="F72" t="n">
-        <v>353.3414428710938</v>
+        <v>2137.41240234375</v>
       </c>
     </row>
     <row r="73">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4037.052702713012</v>
+        <v>27879.796875</v>
       </c>
       <c r="F73" t="n">
-        <v>346.247021484375</v>
+        <v>2185.888916015625</v>
       </c>
     </row>
     <row r="74">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3718.543674659729</v>
+        <v>27128.5453125</v>
       </c>
       <c r="F74" t="n">
-        <v>331.091455078125</v>
+        <v>2456.124609375</v>
       </c>
     </row>
     <row r="75">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3666.503745031357</v>
+        <v>23854.83046875</v>
       </c>
       <c r="F75" t="n">
-        <v>319.3859619140625</v>
+        <v>2453.432373046875</v>
       </c>
     </row>
     <row r="76">
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3451.894582486153</v>
+        <v>19450.241015625</v>
       </c>
       <c r="F76" t="n">
-        <v>339.725537109375</v>
+        <v>1846.725</v>
       </c>
     </row>
     <row r="77">
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3323.747891521454</v>
+        <v>15299.204296875</v>
       </c>
       <c r="F77" t="n">
-        <v>327.518115234375</v>
+        <v>1008.112939453125</v>
       </c>
     </row>
     <row r="78">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2228.848145914078</v>
+        <v>7240.1279296875</v>
       </c>
       <c r="F78" t="n">
-        <v>285.5584350585937</v>
+        <v>665.8820068359374</v>
       </c>
     </row>
     <row r="79">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2197.506020307541</v>
+        <v>7032.5314453125</v>
       </c>
       <c r="F79" t="n">
-        <v>294.44296875</v>
+        <v>1017.755859375</v>
       </c>
     </row>
     <row r="80">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2197.506020307541</v>
+        <v>2061.87861328125</v>
       </c>
       <c r="F80" t="n">
-        <v>294.44296875</v>
+        <v>248.6247253417969</v>
       </c>
     </row>
     <row r="81">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2099.071509039402</v>
+        <v>425.681103515625</v>
       </c>
       <c r="F81" t="n">
-        <v>276.1872802734374</v>
+        <v>82.57717895507812</v>
       </c>
     </row>
     <row r="82">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5260.692680969239</v>
+        <v>36050.72625</v>
       </c>
       <c r="F82" t="n">
-        <v>424.0097314453125</v>
+        <v>2564.8948828125</v>
       </c>
     </row>
     <row r="83">
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4844.463243255615</v>
+        <v>33455.75625</v>
       </c>
       <c r="F83" t="n">
-        <v>415.49642578125</v>
+        <v>2623.066699218751</v>
       </c>
     </row>
     <row r="84">
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4462.252409591674</v>
+        <v>32554.254375</v>
       </c>
       <c r="F84" t="n">
-        <v>397.30974609375</v>
+        <v>2947.34953125</v>
       </c>
     </row>
     <row r="85">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4399.804494037629</v>
+        <v>28625.7965625</v>
       </c>
       <c r="F85" t="n">
-        <v>383.2631542968751</v>
+        <v>2944.118847656249</v>
       </c>
     </row>
     <row r="86">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4142.273498983383</v>
+        <v>23340.28921875</v>
       </c>
       <c r="F86" t="n">
-        <v>407.67064453125</v>
+        <v>2216.07</v>
       </c>
     </row>
     <row r="87">
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3988.497469825745</v>
+        <v>18359.04515625</v>
       </c>
       <c r="F87" t="n">
-        <v>393.02173828125</v>
+        <v>1209.73552734375</v>
       </c>
     </row>
     <row r="88">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2674.617775096893</v>
+        <v>8688.153515624999</v>
       </c>
       <c r="F88" t="n">
-        <v>342.6701220703125</v>
+        <v>799.0584082031249</v>
       </c>
     </row>
     <row r="89">
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2637.007224369049</v>
+        <v>8439.037734375001</v>
       </c>
       <c r="F89" t="n">
-        <v>353.3315625</v>
+        <v>1221.30703125</v>
       </c>
     </row>
     <row r="90">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2637.007224369049</v>
+        <v>2474.2543359375</v>
       </c>
       <c r="F90" t="n">
-        <v>353.3315625</v>
+        <v>298.3496704101563</v>
       </c>
     </row>
     <row r="91">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2518.885810847282</v>
+        <v>510.81732421875</v>
       </c>
       <c r="F91" t="n">
-        <v>331.4247363281249</v>
+        <v>99.09261474609374</v>
       </c>
     </row>
   </sheetData>

--- a/results/q4_output/未来需求推演.xlsx
+++ b/results/q4_output/未来需求推演.xlsx
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25035.2265625</v>
+        <v>17007</v>
       </c>
       <c r="F2" t="n">
-        <v>1781.177001953125</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="3">
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23233.1640625</v>
+        <v>15620</v>
       </c>
       <c r="F3" t="n">
-        <v>1821.574096679688</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22607.12109375</v>
+        <v>12314</v>
       </c>
       <c r="F4" t="n">
-        <v>2046.7705078125</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="5">
@@ -546,14 +546,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19879.025390625</v>
+        <v>17634</v>
       </c>
       <c r="F5" t="n">
-        <v>2044.526977539062</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="6">
@@ -570,14 +570,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16208.5341796875</v>
+        <v>15916</v>
       </c>
       <c r="F6" t="n">
-        <v>1538.9375</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="7">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12749.3369140625</v>
+        <v>15733</v>
       </c>
       <c r="F7" t="n">
-        <v>840.0941162109375</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="8">
@@ -618,14 +618,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6033.43994140625</v>
+        <v>7585</v>
       </c>
       <c r="F8" t="n">
-        <v>554.9016723632812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="9">
@@ -642,14 +642,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5860.44287109375</v>
+        <v>7788</v>
       </c>
       <c r="F9" t="n">
-        <v>848.1298828125</v>
+        <v>974</v>
       </c>
     </row>
     <row r="10">
@@ -666,14 +666,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1718.232177734375</v>
+        <v>17379</v>
       </c>
       <c r="F10" t="n">
-        <v>207.1872711181641</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="11">
@@ -690,14 +690,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>354.7342529296875</v>
+        <v>9297</v>
       </c>
       <c r="F11" t="n">
-        <v>68.81431579589844</v>
+        <v>991</v>
       </c>
     </row>
     <row r="12">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>27538.74921875</v>
+        <v>18707.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1959.294702148438</v>
+        <v>2326.5</v>
       </c>
     </row>
     <row r="13">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25556.48046875</v>
+        <v>17182</v>
       </c>
       <c r="F13" t="n">
-        <v>2003.731506347657</v>
+        <v>2128.5</v>
       </c>
     </row>
     <row r="14">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>24867.833203125</v>
+        <v>13545.4</v>
       </c>
       <c r="F14" t="n">
-        <v>2251.44755859375</v>
+        <v>1780.9</v>
       </c>
     </row>
     <row r="15">
@@ -786,14 +786,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21866.9279296875</v>
+        <v>19397.4</v>
       </c>
       <c r="F15" t="n">
-        <v>2248.979675292968</v>
+        <v>1995.4</v>
       </c>
     </row>
     <row r="16">
@@ -810,14 +810,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>17829.38759765625</v>
+        <v>17507.6</v>
       </c>
       <c r="F16" t="n">
-        <v>1692.83125</v>
+        <v>2119.7</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14024.27060546875</v>
+        <v>17306.3</v>
       </c>
       <c r="F17" t="n">
-        <v>924.1035278320313</v>
+        <v>1898.6</v>
       </c>
     </row>
     <row r="18">
@@ -858,14 +858,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6636.783935546876</v>
+        <v>8343.5</v>
       </c>
       <c r="F18" t="n">
-        <v>610.3918395996094</v>
+        <v>886.6</v>
       </c>
     </row>
     <row r="19">
@@ -882,14 +882,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446.487158203126</v>
+        <v>8566.800000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>932.9428710937501</v>
+        <v>1071.4</v>
       </c>
     </row>
     <row r="20">
@@ -906,14 +906,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1890.055395507813</v>
+        <v>19116.9</v>
       </c>
       <c r="F20" t="n">
-        <v>227.9059982299805</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="21">
@@ -930,14 +930,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>390.2076782226563</v>
+        <v>10226.7</v>
       </c>
       <c r="F21" t="n">
-        <v>75.69574737548828</v>
+        <v>1090.1</v>
       </c>
     </row>
     <row r="22">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>30292.624140625</v>
+        <v>20578.47</v>
       </c>
       <c r="F22" t="n">
-        <v>2155.224172363281</v>
+        <v>2559.150000000001</v>
       </c>
     </row>
     <row r="23">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>28112.12851562501</v>
+        <v>18900.2</v>
       </c>
       <c r="F23" t="n">
-        <v>2204.104656982423</v>
+        <v>2341.35</v>
       </c>
     </row>
     <row r="24">
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>27354.6165234375</v>
+        <v>14899.94</v>
       </c>
       <c r="F24" t="n">
-        <v>2476.592314453125</v>
+        <v>1958.99</v>
       </c>
     </row>
     <row r="25">
@@ -1026,14 +1026,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24053.62072265625</v>
+        <v>21337.14</v>
       </c>
       <c r="F25" t="n">
-        <v>2473.877642822265</v>
+        <v>2194.940000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1050,14 +1050,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>19612.32635742188</v>
+        <v>19258.36</v>
       </c>
       <c r="F26" t="n">
-        <v>1862.114375</v>
+        <v>2331.670000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15426.69766601563</v>
+        <v>19036.93</v>
       </c>
       <c r="F27" t="n">
-        <v>1016.513880615234</v>
+        <v>2088.46</v>
       </c>
     </row>
     <row r="28">
@@ -1098,14 +1098,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>7300.462329101563</v>
+        <v>9177.850000000002</v>
       </c>
       <c r="F28" t="n">
-        <v>671.4310235595705</v>
+        <v>975.2600000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1122,14 +1122,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7091.135874023438</v>
+        <v>9423.480000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>1026.237158203125</v>
+        <v>1178.54</v>
       </c>
     </row>
     <row r="30">
@@ -1146,14 +1146,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079.060935058594</v>
+        <v>21028.59</v>
       </c>
       <c r="F30" t="n">
-        <v>250.6965980529786</v>
+        <v>2855.6</v>
       </c>
     </row>
     <row r="31">
@@ -1170,14 +1170,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>429.228446044922</v>
+        <v>11249.37</v>
       </c>
       <c r="F31" t="n">
-        <v>83.26532211303713</v>
+        <v>1199.11</v>
       </c>
     </row>
     <row r="32">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>25035.2265625</v>
+        <v>17007</v>
       </c>
       <c r="F32" t="n">
-        <v>1781.177001953125</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="33">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>23233.1640625</v>
+        <v>15620</v>
       </c>
       <c r="F33" t="n">
-        <v>1821.574096679688</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="34">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>22607.12109375</v>
+        <v>12314</v>
       </c>
       <c r="F34" t="n">
-        <v>2046.7705078125</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="35">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>19879.025390625</v>
+        <v>17634</v>
       </c>
       <c r="F35" t="n">
-        <v>2044.526977539062</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="36">
@@ -1290,14 +1290,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>16208.5341796875</v>
+        <v>15916</v>
       </c>
       <c r="F36" t="n">
-        <v>1538.9375</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="37">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>12749.3369140625</v>
+        <v>15733</v>
       </c>
       <c r="F37" t="n">
-        <v>840.0941162109375</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="38">
@@ -1338,14 +1338,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6033.43994140625</v>
+        <v>7585</v>
       </c>
       <c r="F38" t="n">
-        <v>554.9016723632812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="39">
@@ -1362,14 +1362,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5860.44287109375</v>
+        <v>7788</v>
       </c>
       <c r="F39" t="n">
-        <v>848.1298828125</v>
+        <v>974</v>
       </c>
     </row>
     <row r="40">
@@ -1386,14 +1386,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1718.232177734375</v>
+        <v>17379</v>
       </c>
       <c r="F40" t="n">
-        <v>207.1872711181641</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="41">
@@ -1410,14 +1410,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>354.7342529296875</v>
+        <v>9297</v>
       </c>
       <c r="F41" t="n">
-        <v>68.81431579589844</v>
+        <v>991</v>
       </c>
     </row>
     <row r="42">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>28790.510546875</v>
+        <v>19558.05</v>
       </c>
       <c r="F42" t="n">
-        <v>2048.353552246093</v>
+        <v>2432.25</v>
       </c>
     </row>
     <row r="43">
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>26718.138671875</v>
+        <v>17963</v>
       </c>
       <c r="F43" t="n">
-        <v>2094.810211181641</v>
+        <v>2225.25</v>
       </c>
     </row>
     <row r="44">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25998.1892578125</v>
+        <v>14161.1</v>
       </c>
       <c r="F44" t="n">
-        <v>2353.786083984375</v>
+        <v>1861.85</v>
       </c>
     </row>
     <row r="45">
@@ -1506,14 +1506,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>22860.87919921875</v>
+        <v>20279.1</v>
       </c>
       <c r="F45" t="n">
-        <v>2351.206024169921</v>
+        <v>2086.1</v>
       </c>
     </row>
     <row r="46">
@@ -1530,14 +1530,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>18639.81430664062</v>
+        <v>18303.4</v>
       </c>
       <c r="F46" t="n">
-        <v>1769.778125</v>
+        <v>2216.05</v>
       </c>
     </row>
     <row r="47">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>14661.73745117187</v>
+        <v>18092.95</v>
       </c>
       <c r="F47" t="n">
-        <v>966.1082336425781</v>
+        <v>1984.9</v>
       </c>
     </row>
     <row r="48">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6938.455932617187</v>
+        <v>8722.75</v>
       </c>
       <c r="F48" t="n">
-        <v>638.1369232177734</v>
+        <v>926.9</v>
       </c>
     </row>
     <row r="49">
@@ -1602,14 +1602,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6739.509301757812</v>
+        <v>8956.199999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>975.3493652343749</v>
+        <v>1120.1</v>
       </c>
     </row>
     <row r="50">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1975.967004394531</v>
+        <v>19985.85</v>
       </c>
       <c r="F50" t="n">
-        <v>238.2653617858887</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="51">
@@ -1650,14 +1650,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>407.9443908691406</v>
+        <v>10691.55</v>
       </c>
       <c r="F51" t="n">
-        <v>79.1364631652832</v>
+        <v>1139.65</v>
       </c>
     </row>
     <row r="52">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>33109.08712890624</v>
+        <v>22491.7575</v>
       </c>
       <c r="F52" t="n">
-        <v>2355.606585083007</v>
+        <v>2797.0875</v>
       </c>
     </row>
     <row r="53">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>30725.85947265624</v>
+        <v>20657.45</v>
       </c>
       <c r="F53" t="n">
-        <v>2409.031742858887</v>
+        <v>2559.037499999999</v>
       </c>
     </row>
     <row r="54">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>29897.91764648437</v>
+        <v>16285.265</v>
       </c>
       <c r="F54" t="n">
-        <v>2706.853996582031</v>
+        <v>2141.1275</v>
       </c>
     </row>
     <row r="55">
@@ -1746,14 +1746,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>26290.01107910156</v>
+        <v>23320.965</v>
       </c>
       <c r="F55" t="n">
-        <v>2703.886927795409</v>
+        <v>2399.014999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1770,14 +1770,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>21435.78645263672</v>
+        <v>21048.91</v>
       </c>
       <c r="F56" t="n">
-        <v>2035.24484375</v>
+        <v>2548.4575</v>
       </c>
     </row>
     <row r="57">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>16860.99806884765</v>
+        <v>20806.8925</v>
       </c>
       <c r="F57" t="n">
-        <v>1111.024468688965</v>
+        <v>2282.635</v>
       </c>
     </row>
     <row r="58">
@@ -1818,14 +1818,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7979.224322509765</v>
+        <v>10031.1625</v>
       </c>
       <c r="F58" t="n">
-        <v>733.8574617004393</v>
+        <v>1065.935</v>
       </c>
     </row>
     <row r="59">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>7750.435697021483</v>
+        <v>10299.63</v>
       </c>
       <c r="F59" t="n">
-        <v>1121.651770019531</v>
+        <v>1288.115</v>
       </c>
     </row>
     <row r="60">
@@ -1866,14 +1866,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2272.362055053711</v>
+        <v>22983.7275</v>
       </c>
       <c r="F60" t="n">
-        <v>274.005166053772</v>
+        <v>3121.099999999999</v>
       </c>
     </row>
     <row r="61">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>469.1360494995117</v>
+        <v>12295.2825</v>
       </c>
       <c r="F61" t="n">
-        <v>91.00693264007568</v>
+        <v>1310.5975</v>
       </c>
     </row>
     <row r="62">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>25035.2265625</v>
+        <v>17007</v>
       </c>
       <c r="F62" t="n">
-        <v>1781.177001953125</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="63">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>23233.1640625</v>
+        <v>15620</v>
       </c>
       <c r="F63" t="n">
-        <v>1821.574096679688</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="64">
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>22607.12109375</v>
+        <v>12314</v>
       </c>
       <c r="F64" t="n">
-        <v>2046.7705078125</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="65">
@@ -1986,14 +1986,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>19879.025390625</v>
+        <v>17634</v>
       </c>
       <c r="F65" t="n">
-        <v>2044.526977539062</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="66">
@@ -2010,14 +2010,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>16208.5341796875</v>
+        <v>15916</v>
       </c>
       <c r="F66" t="n">
-        <v>1538.9375</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="67">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>12749.3369140625</v>
+        <v>15733</v>
       </c>
       <c r="F67" t="n">
-        <v>840.0941162109375</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="68">
@@ -2058,14 +2058,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6033.43994140625</v>
+        <v>7585</v>
       </c>
       <c r="F68" t="n">
-        <v>554.9016723632812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="69">
@@ -2082,14 +2082,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5860.44287109375</v>
+        <v>7788</v>
       </c>
       <c r="F69" t="n">
-        <v>848.1298828125</v>
+        <v>974</v>
       </c>
     </row>
     <row r="70">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1718.232177734375</v>
+        <v>17379</v>
       </c>
       <c r="F70" t="n">
-        <v>207.1872711181641</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="71">
@@ -2130,14 +2130,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>354.7342529296875</v>
+        <v>9297</v>
       </c>
       <c r="F71" t="n">
-        <v>68.81431579589844</v>
+        <v>991</v>
       </c>
     </row>
     <row r="72">
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>30042.271875</v>
+        <v>20408.4</v>
       </c>
       <c r="F72" t="n">
-        <v>2137.41240234375</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="73">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>27879.796875</v>
+        <v>18744</v>
       </c>
       <c r="F73" t="n">
-        <v>2185.888916015625</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="74">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>27128.5453125</v>
+        <v>14776.8</v>
       </c>
       <c r="F74" t="n">
-        <v>2456.124609375</v>
+        <v>1942.8</v>
       </c>
     </row>
     <row r="75">
@@ -2226,14 +2226,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>23854.83046875</v>
+        <v>21160.8</v>
       </c>
       <c r="F75" t="n">
-        <v>2453.432373046875</v>
+        <v>2176.8</v>
       </c>
     </row>
     <row r="76">
@@ -2250,14 +2250,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>19450.241015625</v>
+        <v>19099.2</v>
       </c>
       <c r="F76" t="n">
-        <v>1846.725</v>
+        <v>2312.4</v>
       </c>
     </row>
     <row r="77">
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>15299.204296875</v>
+        <v>18879.6</v>
       </c>
       <c r="F77" t="n">
-        <v>1008.112939453125</v>
+        <v>2071.2</v>
       </c>
     </row>
     <row r="78">
@@ -2298,14 +2298,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>7240.1279296875</v>
+        <v>9102</v>
       </c>
       <c r="F78" t="n">
-        <v>665.8820068359374</v>
+        <v>967.1999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -2322,14 +2322,14 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>7032.5314453125</v>
+        <v>9345.6</v>
       </c>
       <c r="F79" t="n">
-        <v>1017.755859375</v>
+        <v>1168.8</v>
       </c>
     </row>
     <row r="80">
@@ -2346,14 +2346,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2061.87861328125</v>
+        <v>20854.8</v>
       </c>
       <c r="F80" t="n">
-        <v>248.6247253417969</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="81">
@@ -2370,14 +2370,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>425.681103515625</v>
+        <v>11156.4</v>
       </c>
       <c r="F81" t="n">
-        <v>82.57717895507812</v>
+        <v>1189.2</v>
       </c>
     </row>
     <row r="82">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>36050.72625</v>
+        <v>24490.08</v>
       </c>
       <c r="F82" t="n">
-        <v>2564.8948828125</v>
+        <v>3045.6</v>
       </c>
     </row>
     <row r="83">
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>33455.75625</v>
+        <v>22492.8</v>
       </c>
       <c r="F83" t="n">
-        <v>2623.066699218751</v>
+        <v>2786.4</v>
       </c>
     </row>
     <row r="84">
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>32554.254375</v>
+        <v>17732.16</v>
       </c>
       <c r="F84" t="n">
-        <v>2947.34953125</v>
+        <v>2331.36</v>
       </c>
     </row>
     <row r="85">
@@ -2466,14 +2466,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>28625.7965625</v>
+        <v>25392.96</v>
       </c>
       <c r="F85" t="n">
-        <v>2944.118847656249</v>
+        <v>2612.16</v>
       </c>
     </row>
     <row r="86">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>23340.28921875</v>
+        <v>22919.04</v>
       </c>
       <c r="F86" t="n">
-        <v>2216.07</v>
+        <v>2774.88</v>
       </c>
     </row>
     <row r="87">
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>18359.04515625</v>
+        <v>22655.52</v>
       </c>
       <c r="F87" t="n">
-        <v>1209.73552734375</v>
+        <v>2485.44</v>
       </c>
     </row>
     <row r="88">
@@ -2538,14 +2538,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>8688.153515624999</v>
+        <v>10922.4</v>
       </c>
       <c r="F88" t="n">
-        <v>799.0584082031249</v>
+        <v>1160.64</v>
       </c>
     </row>
     <row r="89">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>8439.037734375001</v>
+        <v>11214.72</v>
       </c>
       <c r="F89" t="n">
-        <v>1221.30703125</v>
+        <v>1402.56</v>
       </c>
     </row>
     <row r="90">
@@ -2586,14 +2586,14 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2474.2543359375</v>
+        <v>25025.76</v>
       </c>
       <c r="F90" t="n">
-        <v>298.3496704101563</v>
+        <v>3398.4</v>
       </c>
     </row>
     <row r="91">
@@ -2610,14 +2610,14 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>510.81732421875</v>
+        <v>13387.68</v>
       </c>
       <c r="F91" t="n">
-        <v>99.09261474609374</v>
+        <v>1427.04</v>
       </c>
     </row>
   </sheetData>
